--- a/monday_plan.xlsx
+++ b/monday_plan.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3504" uniqueCount="1842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3509" uniqueCount="1846">
   <si>
     <t xml:space="preserve">monday.com Operating Plan, Q3 2026-Q4 2027 (Phase 3b) - DRAFT FOR OWNER REVIEW, NOT FROZEN</t>
   </si>
@@ -3120,6 +3120,18 @@
   </si>
   <si>
     <t xml:space="preserve">Added Trigger_History: fires, confirmed and false alarms over the last 20 quarters for T1-T3, and the derivation of 1.48% and 194. P14 Base/Downside are now formulas (last-8 median / minimum) instead of typed numbers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRE-REGISTERED trigger 1 definition (revision 2, item 2), written before any test was computed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue trigger: actual quarterly revenue is more than the average 1-quarter-ahead backtest miss (1.04%, linked to the Backtest sheet) below the Base path, for two consecutive quarters.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner instruction: replace the absolute-threshold T1; test only on the 8 backtest quarters; do not tune the threshold to history.</t>
   </si>
   <si>
     <t xml:space="preserve">C8</t>
@@ -13126,7 +13138,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -13458,9 +13470,26 @@
         <v>1030</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>1012</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E22" s="10" t="s">
         <v>1008</v>
       </c>
     </row>
@@ -13494,18 +13523,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>262</v>
@@ -13514,10 +13543,10 @@
         <v>261</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>17</v>
@@ -13525,13 +13554,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>66</v>
@@ -13554,13 +13583,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>67</v>
@@ -13583,13 +13612,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>1042</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>1038</v>
-      </c>
       <c r="C6" s="10" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>68</v>
@@ -13612,13 +13641,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>69</v>
@@ -13641,13 +13670,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>70</v>
@@ -13670,13 +13699,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>71</v>
@@ -13699,13 +13728,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>72</v>
@@ -13728,13 +13757,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>73</v>
@@ -13757,13 +13786,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>74</v>
@@ -13786,13 +13815,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>75</v>
@@ -13815,13 +13844,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>76</v>
@@ -13844,13 +13873,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>77</v>
@@ -13873,13 +13902,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>78</v>
@@ -13902,13 +13931,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>79</v>
@@ -13931,13 +13960,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>81</v>
@@ -13960,13 +13989,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>82</v>
@@ -13989,13 +14018,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>83</v>
@@ -14018,13 +14047,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>84</v>
@@ -14047,13 +14076,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>85</v>
@@ -14076,13 +14105,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>86</v>
@@ -14105,13 +14134,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>87</v>
@@ -14134,13 +14163,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>88</v>
@@ -14163,13 +14192,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>89</v>
@@ -14192,13 +14221,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>90</v>
@@ -14221,13 +14250,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>91</v>
@@ -14250,13 +14279,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>92</v>
@@ -14279,13 +14308,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>93</v>
@@ -14308,13 +14337,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>94</v>
@@ -14337,13 +14366,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>96</v>
@@ -14366,13 +14395,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>97</v>
@@ -14395,13 +14424,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>98</v>
@@ -14424,13 +14453,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>99</v>
@@ -14453,13 +14482,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>100</v>
@@ -14482,13 +14511,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>101</v>
@@ -14511,13 +14540,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>102</v>
@@ -14540,13 +14569,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>103</v>
@@ -14569,13 +14598,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>104</v>
@@ -14598,13 +14627,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>105</v>
@@ -14627,13 +14656,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>106</v>
@@ -14656,13 +14685,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>107</v>
@@ -14685,13 +14714,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>108</v>
@@ -14714,13 +14743,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>109</v>
@@ -14743,13 +14772,13 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>111</v>
@@ -14772,13 +14801,13 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>112</v>
@@ -14801,13 +14830,13 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>113</v>
@@ -14830,13 +14859,13 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>114</v>
@@ -14859,13 +14888,13 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>115</v>
@@ -14888,13 +14917,13 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>116</v>
@@ -14917,13 +14946,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>117</v>
@@ -14946,13 +14975,13 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>118</v>
@@ -14975,13 +15004,13 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>119</v>
@@ -15004,13 +15033,13 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>120</v>
@@ -15033,13 +15062,13 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>121</v>
@@ -15062,13 +15091,13 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>122</v>
@@ -15091,13 +15120,13 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>123</v>
@@ -15120,13 +15149,13 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>124</v>
@@ -15149,13 +15178,13 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>126</v>
@@ -15178,13 +15207,13 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>127</v>
@@ -15207,13 +15236,13 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>128</v>
@@ -15236,13 +15265,13 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>129</v>
@@ -15265,13 +15294,13 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>130</v>
@@ -15294,13 +15323,13 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>131</v>
@@ -15323,13 +15352,13 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>132</v>
@@ -15352,13 +15381,13 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>133</v>
@@ -15381,13 +15410,13 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>134</v>
@@ -15410,13 +15439,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>135</v>
@@ -15439,13 +15468,13 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>136</v>
@@ -15468,13 +15497,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>137</v>
@@ -15497,13 +15526,13 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>138</v>
@@ -15526,13 +15555,13 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>139</v>
@@ -15555,13 +15584,13 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>141</v>
@@ -15584,13 +15613,13 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>142</v>
@@ -15613,13 +15642,13 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>143</v>
@@ -15642,13 +15671,13 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>144</v>
@@ -15671,13 +15700,13 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>145</v>
@@ -15700,13 +15729,13 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>146</v>
@@ -15729,13 +15758,13 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>147</v>
@@ -15758,13 +15787,13 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>148</v>
@@ -15787,13 +15816,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>149</v>
@@ -15816,13 +15845,13 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>150</v>
@@ -15845,13 +15874,13 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>151</v>
@@ -15874,13 +15903,13 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>152</v>
@@ -15903,13 +15932,13 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>153</v>
@@ -15932,13 +15961,13 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>154</v>
@@ -15961,13 +15990,13 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>156</v>
@@ -15990,13 +16019,13 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>157</v>
@@ -16019,13 +16048,13 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>158</v>
@@ -16048,13 +16077,13 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>159</v>
@@ -16077,13 +16106,13 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>160</v>
@@ -16106,13 +16135,13 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>161</v>
@@ -16135,13 +16164,13 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>162</v>
@@ -16164,13 +16193,13 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="10" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>163</v>
@@ -16193,13 +16222,13 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>164</v>
@@ -16222,13 +16251,13 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>165</v>
@@ -16251,13 +16280,13 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="D98" s="10" t="s">
         <v>166</v>
@@ -16280,13 +16309,13 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>167</v>
@@ -16309,13 +16338,13 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>168</v>
@@ -16338,13 +16367,13 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="10" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="D101" s="10" t="s">
         <v>169</v>
@@ -16367,13 +16396,13 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="10" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="D102" s="10" t="s">
         <v>171</v>
@@ -16396,13 +16425,13 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="D103" s="10" t="s">
         <v>172</v>
@@ -16425,13 +16454,13 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="10" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="D104" s="10" t="s">
         <v>173</v>
@@ -16454,13 +16483,13 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="D105" s="10" t="s">
         <v>174</v>
@@ -16483,13 +16512,13 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>175</v>
@@ -16512,13 +16541,13 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>176</v>
@@ -16541,13 +16570,13 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>177</v>
@@ -16570,13 +16599,13 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="10" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>178</v>
@@ -16599,13 +16628,13 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>179</v>
@@ -16628,13 +16657,13 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="D111" s="10" t="s">
         <v>180</v>
@@ -16657,13 +16686,13 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="10" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="D112" s="10" t="s">
         <v>181</v>
@@ -16686,13 +16715,13 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="10" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="D113" s="10" t="s">
         <v>182</v>
@@ -16715,13 +16744,13 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="D114" s="10" t="s">
         <v>183</v>
@@ -16744,13 +16773,13 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="10" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="D115" s="10" t="s">
         <v>184</v>
@@ -16773,13 +16802,13 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>187</v>
@@ -16802,13 +16831,13 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="10" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>189</v>
@@ -16831,13 +16860,13 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="10" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="D118" s="10" t="s">
         <v>190</v>
@@ -16860,13 +16889,13 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="10" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>191</v>
@@ -16889,13 +16918,13 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="D120" s="10" t="s">
         <v>192</v>
@@ -16918,13 +16947,13 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="D121" s="10" t="s">
         <v>193</v>
@@ -16947,13 +16976,13 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="10" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="D122" s="10" t="s">
         <v>194</v>
@@ -16976,13 +17005,13 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="10" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="D123" s="10" t="s">
         <v>195</v>
@@ -17005,13 +17034,13 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="10" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="D124" s="10" t="s">
         <v>196</v>
@@ -17034,13 +17063,13 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="10" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="D125" s="10" t="s">
         <v>197</v>
@@ -17063,13 +17092,13 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="10" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="D126" s="10" t="s">
         <v>198</v>
@@ -17092,13 +17121,13 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="10" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="D127" s="10" t="s">
         <v>199</v>
@@ -17121,13 +17150,13 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="10" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D128" s="10" t="s">
         <v>200</v>
@@ -17150,13 +17179,13 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="10" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="D129" s="10" t="s">
         <v>201</v>
@@ -17179,13 +17208,13 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="10" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="D130" s="10" t="s">
         <v>202</v>
@@ -17208,13 +17237,13 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="10" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="D131" s="10" t="s">
         <v>204</v>
@@ -17237,13 +17266,13 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="10" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="D132" s="10" t="s">
         <v>205</v>
@@ -17266,13 +17295,13 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="10" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="D133" s="10" t="s">
         <v>206</v>
@@ -17295,13 +17324,13 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="10" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="D134" s="10" t="s">
         <v>207</v>
@@ -17324,13 +17353,13 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="10" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="D135" s="10" t="s">
         <v>208</v>
@@ -17353,13 +17382,13 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="10" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="D136" s="10" t="s">
         <v>209</v>
@@ -17382,13 +17411,13 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="10" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="D137" s="10" t="s">
         <v>210</v>
@@ -17411,13 +17440,13 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="10" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="D138" s="10" t="s">
         <v>211</v>
@@ -17440,13 +17469,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="10" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="D139" s="10" t="s">
         <v>212</v>
@@ -17469,13 +17498,13 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="10" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="D140" s="10" t="s">
         <v>213</v>
@@ -17498,13 +17527,13 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="10" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="D141" s="10" t="s">
         <v>214</v>
@@ -17527,13 +17556,13 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="10" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="D142" s="10" t="s">
         <v>215</v>
@@ -17556,13 +17585,13 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="10" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="D143" s="10" t="s">
         <v>216</v>
@@ -17585,13 +17614,13 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="10" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="D144" s="10" t="s">
         <v>217</v>
@@ -17614,13 +17643,13 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="10" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="D145" s="10" t="s">
         <v>219</v>
@@ -17643,13 +17672,13 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="10" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="D146" s="10" t="s">
         <v>220</v>
@@ -17672,13 +17701,13 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="10" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="D147" s="10" t="s">
         <v>221</v>
@@ -17701,13 +17730,13 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="10" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="D148" s="10" t="s">
         <v>222</v>
@@ -17730,13 +17759,13 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="10" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="D149" s="10" t="s">
         <v>223</v>
@@ -17759,13 +17788,13 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="10" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="D150" s="10" t="s">
         <v>224</v>
@@ -17788,13 +17817,13 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="10" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="D151" s="10" t="s">
         <v>225</v>
@@ -17817,13 +17846,13 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="10" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="D152" s="10" t="s">
         <v>226</v>
@@ -17846,13 +17875,13 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="10" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="D153" s="10" t="s">
         <v>228</v>
@@ -17875,13 +17904,13 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="10" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="D154" s="10" t="s">
         <v>229</v>
@@ -17904,13 +17933,13 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="10" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="D155" s="10" t="s">
         <v>230</v>
@@ -17933,13 +17962,13 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="10" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="D156" s="10" t="s">
         <v>231</v>
@@ -17962,13 +17991,13 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="10" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="D157" s="10" t="s">
         <v>232</v>
@@ -17991,13 +18020,13 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="10" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="D158" s="10" t="s">
         <v>233</v>
@@ -18020,13 +18049,13 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="10" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="D159" s="10" t="s">
         <v>234</v>
@@ -18049,13 +18078,13 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="10" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="D160" s="10" t="s">
         <v>235</v>
@@ -18078,13 +18107,13 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="10" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="D161" s="10" t="s">
         <v>236</v>
@@ -18107,13 +18136,13 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="10" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="D162" s="10" t="s">
         <v>237</v>
@@ -18136,13 +18165,13 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="10" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="D163" s="10" t="s">
         <v>238</v>
@@ -18165,13 +18194,13 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="10" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="D164" s="10" t="s">
         <v>240</v>
@@ -18194,13 +18223,13 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="10" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="D165" s="10" t="s">
         <v>241</v>
@@ -18223,13 +18252,13 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="10" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="D166" s="10" t="s">
         <v>242</v>
@@ -18252,13 +18281,13 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="10" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
       <c r="B167" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="D167" s="10" t="s">
         <v>243</v>
@@ -18281,13 +18310,13 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="10" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="D168" s="10" t="s">
         <v>244</v>
@@ -18310,13 +18339,13 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="10" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="B169" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="D169" s="10" t="s">
         <v>245</v>
@@ -18339,13 +18368,13 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="10" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="D170" s="10" t="s">
         <v>246</v>
@@ -18368,13 +18397,13 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="10" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="D171" s="10" t="s">
         <v>247</v>
@@ -18397,13 +18426,13 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="10" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="D172" s="10" t="s">
         <v>248</v>
@@ -18426,13 +18455,13 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="10" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="D173" s="10" t="s">
         <v>249</v>
@@ -18455,13 +18484,13 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="10" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="D174" s="10" t="s">
         <v>250</v>
@@ -18484,13 +18513,13 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="10" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="D175" s="10" t="s">
         <v>251</v>
@@ -18513,13 +18542,13 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="10" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="D176" s="10" t="s">
         <v>252</v>
@@ -18542,13 +18571,13 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="10" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="D177" s="10" t="s">
         <v>253</v>
@@ -18571,13 +18600,13 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="10" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="D178" s="10" t="s">
         <v>265</v>
@@ -18600,13 +18629,13 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="10" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="D179" s="10" t="s">
         <v>268</v>
@@ -18629,13 +18658,13 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="10" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B180" s="10" t="s">
         <v>1391</v>
       </c>
-      <c r="B180" s="10" t="s">
-        <v>1387</v>
-      </c>
       <c r="C180" s="10" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="D180" s="10" t="s">
         <v>270</v>
@@ -18658,13 +18687,13 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="10" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C181" s="10" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="D181" s="10" t="s">
         <v>272</v>
@@ -18687,13 +18716,13 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="10" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C182" s="10" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="D182" s="10" t="s">
         <v>274</v>
@@ -18716,13 +18745,13 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="10" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C183" s="10" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="D183" s="10" t="s">
         <v>276</v>
@@ -18745,13 +18774,13 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="10" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C184" s="10" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="D184" s="10" t="s">
         <v>278</v>
@@ -18774,13 +18803,13 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="10" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C185" s="10" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="D185" s="10" t="s">
         <v>280</v>
@@ -18803,13 +18832,13 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="10" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C186" s="10" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="D186" s="10" t="s">
         <v>282</v>
@@ -18832,13 +18861,13 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="10" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C187" s="10" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="D187" s="10" t="s">
         <v>284</v>
@@ -18861,13 +18890,13 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="10" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="D188" s="10" t="s">
         <v>286</v>
@@ -18890,13 +18919,13 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="10" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="C189" s="10" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="D189" s="10" t="s">
         <v>289</v>
@@ -18919,13 +18948,13 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="10" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B190" s="10" t="s">
         <v>1412</v>
       </c>
-      <c r="B190" s="10" t="s">
-        <v>1408</v>
-      </c>
       <c r="C190" s="10" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="D190" s="10" t="s">
         <v>291</v>
@@ -18948,13 +18977,13 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="10" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="D191" s="10" t="s">
         <v>293</v>
@@ -18977,13 +19006,13 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="10" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="C192" s="10" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="D192" s="10" t="s">
         <v>295</v>
@@ -19006,13 +19035,13 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="10" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="D193" s="10" t="s">
         <v>297</v>
@@ -19035,13 +19064,13 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="10" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="D194" s="10" t="s">
         <v>299</v>
@@ -19064,13 +19093,13 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="10" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="D195" s="10" t="s">
         <v>302</v>
@@ -19093,13 +19122,13 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="10" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="D196" s="10" t="s">
         <v>304</v>
@@ -19122,13 +19151,13 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="10" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="D197" s="10" t="s">
         <v>306</v>
@@ -19151,13 +19180,13 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="10" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="D198" s="10" t="s">
         <v>309</v>
@@ -19180,13 +19209,13 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="10" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B199" s="10" t="s">
         <v>1431</v>
       </c>
-      <c r="B199" s="10" t="s">
-        <v>1427</v>
-      </c>
       <c r="C199" s="10" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="D199" s="10" t="s">
         <v>311</v>
@@ -19209,13 +19238,13 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="10" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="B200" s="10" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="C200" s="10" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="D200" s="10" t="s">
         <v>313</v>
@@ -19238,13 +19267,13 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="10" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="C201" s="10" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="D201" s="10" t="s">
         <v>315</v>
@@ -19267,13 +19296,13 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="10" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="C202" s="10" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="D202" s="10" t="s">
         <v>317</v>
@@ -19296,13 +19325,13 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="10" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="C203" s="10" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="D203" s="10" t="s">
         <v>319</v>
@@ -19325,13 +19354,13 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="10" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="B204" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C204" s="10" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D204" s="10" t="s">
         <v>342</v>
@@ -19354,13 +19383,13 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="10" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="B205" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C205" s="10" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="D205" s="10" t="s">
         <v>343</v>
@@ -19383,13 +19412,13 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="10" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="B206" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C206" s="10" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="D206" s="10" t="s">
         <v>345</v>
@@ -19412,13 +19441,13 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="10" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="B207" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C207" s="10" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D207" s="10" t="s">
         <v>346</v>
@@ -19441,13 +19470,13 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="10" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="B208" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>348</v>
@@ -19470,13 +19499,13 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="10" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C209" s="10" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="D209" s="10" t="s">
         <v>349</v>
@@ -19499,13 +19528,13 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="10" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="B210" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C210" s="10" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="D210" s="10" t="s">
         <v>351</v>
@@ -19528,13 +19557,13 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="10" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>352</v>
@@ -19557,13 +19586,13 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="10" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="B212" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C212" s="10" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="D212" s="10" t="s">
         <v>202</v>
@@ -19586,13 +19615,13 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="10" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="B213" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C213" s="10" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="D213" s="10" t="s">
         <v>302</v>
@@ -19615,13 +19644,13 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="10" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="B214" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C214" s="10" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="D214" s="10" t="s">
         <v>378</v>
@@ -19644,13 +19673,13 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="10" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="B215" s="10" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="C215" s="10" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="D215" s="10" t="s">
         <v>410</v>
@@ -19673,13 +19702,13 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="10" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="B216" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C216" s="10" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="D216" s="10" t="s">
         <v>860</v>
@@ -19702,13 +19731,13 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="10" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="B217" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C217" s="10" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="D217" s="10" t="s">
         <v>862</v>
@@ -19731,13 +19760,13 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="10" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B218" s="10" t="s">
         <v>1471</v>
       </c>
-      <c r="B218" s="10" t="s">
-        <v>1467</v>
-      </c>
       <c r="C218" s="10" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="D218" s="10" t="s">
         <v>864</v>
@@ -19760,16 +19789,16 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="10" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="B219" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C219" s="10" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="D219" s="10" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="E219" s="17" t="n">
         <f aca="false">Backtest!D7</f>
@@ -19789,16 +19818,16 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="10" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="D220" s="10" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="E220" s="17" t="n">
         <f aca="false">Backtest!E7</f>
@@ -19818,13 +19847,13 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="10" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="D221" s="10" t="s">
         <v>867</v>
@@ -19847,16 +19876,16 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="10" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="D222" s="10" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="E222" s="17" t="n">
         <f aca="false">Backtest!D8</f>
@@ -19876,16 +19905,16 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="10" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="B223" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C223" s="10" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="D223" s="10" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
       <c r="E223" s="17" t="n">
         <f aca="false">Backtest!E8</f>
@@ -19905,13 +19934,13 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="10" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="B224" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="D224" s="10" t="s">
         <v>870</v>
@@ -19934,16 +19963,16 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="10" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="B225" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C225" s="10" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
       <c r="D225" s="10" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="E225" s="17" t="n">
         <f aca="false">Backtest!D9</f>
@@ -19963,16 +19992,16 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="10" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="B226" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C226" s="10" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="D226" s="10" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="E226" s="17" t="n">
         <f aca="false">Backtest!E9</f>
@@ -19992,13 +20021,13 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="10" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="B227" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C227" s="10" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="D227" s="10" t="s">
         <v>873</v>
@@ -20021,16 +20050,16 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="10" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="B228" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C228" s="10" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="D228" s="10" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="E228" s="17" t="n">
         <f aca="false">Backtest!D10</f>
@@ -20050,16 +20079,16 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="10" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="B229" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C229" s="10" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="D229" s="10" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="E229" s="17" t="n">
         <f aca="false">Backtest!E10</f>
@@ -20079,13 +20108,13 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="10" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="B230" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C230" s="10" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="D230" s="10" t="s">
         <v>876</v>
@@ -20108,16 +20137,16 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="10" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="B231" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C231" s="10" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
       <c r="D231" s="10" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="E231" s="17" t="n">
         <f aca="false">Backtest!D11</f>
@@ -20137,16 +20166,16 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="10" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
       <c r="B232" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C232" s="10" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="D232" s="10" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="E232" s="17" t="n">
         <f aca="false">Backtest!E11</f>
@@ -20166,13 +20195,13 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="10" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
       <c r="B233" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C233" s="10" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="D233" s="10" t="s">
         <v>879</v>
@@ -20195,16 +20224,16 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="10" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="B234" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C234" s="10" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="D234" s="10" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="E234" s="17" t="n">
         <f aca="false">Backtest!D12</f>
@@ -20224,16 +20253,16 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="10" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="B235" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C235" s="10" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="D235" s="10" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
       <c r="E235" s="17" t="n">
         <f aca="false">Backtest!E12</f>
@@ -20253,13 +20282,13 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="10" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
       <c r="B236" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C236" s="10" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="D236" s="10" t="s">
         <v>66</v>
@@ -20282,16 +20311,16 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="10" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="B237" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C237" s="10" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
       <c r="D237" s="10" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="E237" s="17" t="n">
         <f aca="false">Backtest!D13</f>
@@ -20311,16 +20340,16 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="10" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="B238" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C238" s="10" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="D238" s="10" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="E238" s="17" t="n">
         <f aca="false">Backtest!E13</f>
@@ -20340,13 +20369,13 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="10" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="B239" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C239" s="10" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="D239" s="10" t="s">
         <v>67</v>
@@ -20369,16 +20398,16 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="10" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="B240" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
       <c r="D240" s="10" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="E240" s="17" t="n">
         <f aca="false">Backtest!D14</f>
@@ -20398,16 +20427,16 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="10" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
       <c r="B241" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C241" s="10" t="s">
-        <v>1533</v>
+        <v>1537</v>
       </c>
       <c r="D241" s="10" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="E241" s="17" t="n">
         <f aca="false">Backtest!E14</f>
@@ -20427,13 +20456,13 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="10" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="B242" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C242" s="10" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="D242" s="10" t="s">
         <v>68</v>
@@ -20456,16 +20485,16 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="10" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="B243" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C243" s="10" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
       <c r="D243" s="10" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
       <c r="E243" s="17" t="n">
         <f aca="false">Backtest!D15</f>
@@ -20485,16 +20514,16 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="10" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="B244" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="D244" s="10" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="E244" s="17" t="n">
         <f aca="false">Backtest!E15</f>
@@ -20514,13 +20543,13 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="10" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C245" s="10" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="D245" s="10" t="s">
         <v>69</v>
@@ -20543,16 +20572,16 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="10" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C246" s="10" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="D246" s="10" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="E246" s="17" t="n">
         <f aca="false">Backtest!D16</f>
@@ -20572,16 +20601,16 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="10" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C247" s="10" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="D247" s="10" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
       <c r="E247" s="17" t="n">
         <f aca="false">Backtest!E16</f>
@@ -20601,13 +20630,13 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="10" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C248" s="10" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="D248" s="10" t="s">
         <v>70</v>
@@ -20630,16 +20659,16 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="10" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C249" s="10" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
       <c r="D249" s="10" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="E249" s="17" t="n">
         <f aca="false">Backtest!D17</f>
@@ -20659,16 +20688,16 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="10" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C250" s="10" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="D250" s="10" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="E250" s="17" t="n">
         <f aca="false">Backtest!E17</f>
@@ -20688,13 +20717,13 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="10" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C251" s="10" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="D251" s="10" t="s">
         <v>71</v>
@@ -20717,16 +20746,16 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="10" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C252" s="10" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="D252" s="10" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="E252" s="17" t="n">
         <f aca="false">Backtest!D18</f>
@@ -20746,16 +20775,16 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="10" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C253" s="10" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="D253" s="10" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="E253" s="17" t="n">
         <f aca="false">Backtest!E18</f>
@@ -20775,13 +20804,13 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="10" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C254" s="10" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="D254" s="10" t="s">
         <v>72</v>
@@ -20804,16 +20833,16 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="10" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C255" s="10" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="D255" s="10" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
       <c r="E255" s="17" t="n">
         <f aca="false">Backtest!D19</f>
@@ -20833,16 +20862,16 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="10" t="s">
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C256" s="10" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
       <c r="D256" s="10" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="E256" s="17" t="n">
         <f aca="false">Backtest!E19</f>
@@ -20862,13 +20891,13 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="10" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="B257" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C257" s="10" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="D257" s="10" t="s">
         <v>73</v>
@@ -20891,16 +20920,16 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="10" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="B258" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C258" s="10" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="D258" s="10" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="E258" s="17" t="n">
         <f aca="false">Backtest!D20</f>
@@ -20920,16 +20949,16 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="10" t="s">
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="B259" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C259" s="10" t="s">
-        <v>1581</v>
+        <v>1585</v>
       </c>
       <c r="D259" s="10" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="E259" s="17" t="n">
         <f aca="false">Backtest!E20</f>
@@ -20949,13 +20978,13 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="10" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C260" s="10" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="D260" s="10" t="s">
         <v>74</v>
@@ -20978,16 +21007,16 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="10" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C261" s="10" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="D261" s="10" t="s">
-        <v>1587</v>
+        <v>1591</v>
       </c>
       <c r="E261" s="17" t="n">
         <f aca="false">Backtest!D21</f>
@@ -21007,16 +21036,16 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="10" t="s">
-        <v>1588</v>
+        <v>1592</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C262" s="10" t="s">
-        <v>1589</v>
+        <v>1593</v>
       </c>
       <c r="D262" s="10" t="s">
-        <v>1590</v>
+        <v>1594</v>
       </c>
       <c r="E262" s="17" t="n">
         <f aca="false">Backtest!E21</f>
@@ -21036,13 +21065,13 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="10" t="s">
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="B263" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C263" s="10" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="D263" s="10" t="s">
         <v>75</v>
@@ -21065,16 +21094,16 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="10" t="s">
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="B264" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C264" s="10" t="s">
-        <v>1594</v>
+        <v>1598</v>
       </c>
       <c r="D264" s="10" t="s">
-        <v>1595</v>
+        <v>1599</v>
       </c>
       <c r="E264" s="17" t="n">
         <f aca="false">Backtest!D22</f>
@@ -21094,16 +21123,16 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="10" t="s">
-        <v>1596</v>
+        <v>1600</v>
       </c>
       <c r="B265" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C265" s="10" t="s">
-        <v>1597</v>
+        <v>1601</v>
       </c>
       <c r="D265" s="10" t="s">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="E265" s="17" t="n">
         <f aca="false">Backtest!E22</f>
@@ -21123,13 +21152,13 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="10" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="B266" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C266" s="10" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="D266" s="10" t="s">
         <v>76</v>
@@ -21152,16 +21181,16 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="10" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="D267" s="10" t="s">
-        <v>1603</v>
+        <v>1607</v>
       </c>
       <c r="E267" s="17" t="n">
         <f aca="false">Backtest!D23</f>
@@ -21181,16 +21210,16 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="10" t="s">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="B268" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C268" s="10" t="s">
-        <v>1605</v>
+        <v>1609</v>
       </c>
       <c r="D268" s="10" t="s">
-        <v>1606</v>
+        <v>1610</v>
       </c>
       <c r="E268" s="17" t="n">
         <f aca="false">Backtest!E23</f>
@@ -21210,13 +21239,13 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="10" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="B269" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C269" s="10" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="D269" s="10" t="s">
         <v>77</v>
@@ -21239,16 +21268,16 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="10" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="B270" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C270" s="10" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="D270" s="10" t="s">
-        <v>1611</v>
+        <v>1615</v>
       </c>
       <c r="E270" s="17" t="n">
         <f aca="false">Backtest!D24</f>
@@ -21268,16 +21297,16 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="10" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="B271" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C271" s="10" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="D271" s="10" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="E271" s="17" t="n">
         <f aca="false">Backtest!E24</f>
@@ -21297,13 +21326,13 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="10" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="B272" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C272" s="10" t="s">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="D272" s="10" t="s">
         <v>78</v>
@@ -21326,16 +21355,16 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="10" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="B273" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C273" s="10" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="D273" s="10" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="E273" s="17" t="n">
         <f aca="false">Backtest!D25</f>
@@ -21355,16 +21384,16 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="10" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="B274" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C274" s="10" t="s">
-        <v>1621</v>
+        <v>1625</v>
       </c>
       <c r="D274" s="10" t="s">
-        <v>1622</v>
+        <v>1626</v>
       </c>
       <c r="E274" s="17" t="n">
         <f aca="false">Backtest!E25</f>
@@ -21384,13 +21413,13 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="10" t="s">
-        <v>1623</v>
+        <v>1627</v>
       </c>
       <c r="B275" s="10" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C275" s="10" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="D275" s="10" t="s">
         <v>79</v>
@@ -21413,16 +21442,16 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="10" t="s">
-        <v>1625</v>
+        <v>1629</v>
       </c>
       <c r="B276" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C276" s="10" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="D276" s="10" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="E276" s="17" t="n">
         <f aca="false">Backtest!D26</f>
@@ -21442,16 +21471,16 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="10" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="B277" s="10" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="C277" s="10" t="s">
-        <v>1629</v>
+        <v>1633</v>
       </c>
       <c r="D277" s="10" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="E277" s="17" t="n">
         <f aca="false">Backtest!E26</f>
@@ -21471,13 +21500,13 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="10" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="B278" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C278" s="10" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="D278" s="10" t="s">
         <v>940</v>
@@ -21500,13 +21529,13 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="10" t="s">
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C279" s="10" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>941</v>
@@ -21529,13 +21558,13 @@
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="10" t="s">
-        <v>1635</v>
+        <v>1639</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C280" s="10" t="s">
-        <v>1636</v>
+        <v>1640</v>
       </c>
       <c r="D280" s="10" t="s">
         <v>942</v>
@@ -21558,13 +21587,13 @@
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="10" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="B281" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C281" s="10" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="D281" s="10" t="s">
         <v>943</v>
@@ -21587,13 +21616,13 @@
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="10" t="s">
-        <v>1639</v>
+        <v>1643</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C282" s="10" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
       <c r="D282" s="10" t="s">
         <v>944</v>
@@ -21616,13 +21645,13 @@
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="10" t="s">
-        <v>1641</v>
+        <v>1645</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C283" s="10" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>945</v>
@@ -21645,13 +21674,13 @@
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="10" t="s">
-        <v>1643</v>
+        <v>1647</v>
       </c>
       <c r="B284" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C284" s="10" t="s">
-        <v>1644</v>
+        <v>1648</v>
       </c>
       <c r="D284" s="10" t="s">
         <v>946</v>
@@ -21674,13 +21703,13 @@
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="10" t="s">
-        <v>1645</v>
+        <v>1649</v>
       </c>
       <c r="B285" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C285" s="10" t="s">
-        <v>1646</v>
+        <v>1650</v>
       </c>
       <c r="D285" s="10" t="s">
         <v>947</v>
@@ -21703,13 +21732,13 @@
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="10" t="s">
-        <v>1647</v>
+        <v>1651</v>
       </c>
       <c r="B286" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C286" s="10" t="s">
-        <v>1648</v>
+        <v>1652</v>
       </c>
       <c r="D286" s="10" t="s">
         <v>240</v>
@@ -21732,13 +21761,13 @@
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="10" t="s">
-        <v>1649</v>
+        <v>1653</v>
       </c>
       <c r="B287" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C287" s="10" t="s">
-        <v>1650</v>
+        <v>1654</v>
       </c>
       <c r="D287" s="10" t="s">
         <v>241</v>
@@ -21761,13 +21790,13 @@
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="10" t="s">
-        <v>1651</v>
+        <v>1655</v>
       </c>
       <c r="B288" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C288" s="10" t="s">
-        <v>1652</v>
+        <v>1656</v>
       </c>
       <c r="D288" s="10" t="s">
         <v>242</v>
@@ -21790,13 +21819,13 @@
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="10" t="s">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="B289" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C289" s="10" t="s">
-        <v>1654</v>
+        <v>1658</v>
       </c>
       <c r="D289" s="10" t="s">
         <v>243</v>
@@ -21819,13 +21848,13 @@
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="10" t="s">
-        <v>1655</v>
+        <v>1659</v>
       </c>
       <c r="B290" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C290" s="10" t="s">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="D290" s="10" t="s">
         <v>244</v>
@@ -21848,13 +21877,13 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="10" t="s">
-        <v>1657</v>
+        <v>1661</v>
       </c>
       <c r="B291" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C291" s="10" t="s">
-        <v>1658</v>
+        <v>1662</v>
       </c>
       <c r="D291" s="10" t="s">
         <v>245</v>
@@ -21877,13 +21906,13 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="10" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="B292" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C292" s="10" t="s">
-        <v>1660</v>
+        <v>1664</v>
       </c>
       <c r="D292" s="10" t="s">
         <v>246</v>
@@ -21906,13 +21935,13 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="10" t="s">
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="B293" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C293" s="10" t="s">
-        <v>1662</v>
+        <v>1666</v>
       </c>
       <c r="D293" s="10" t="s">
         <v>247</v>
@@ -21935,13 +21964,13 @@
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="10" t="s">
-        <v>1663</v>
+        <v>1667</v>
       </c>
       <c r="B294" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C294" s="10" t="s">
-        <v>1664</v>
+        <v>1668</v>
       </c>
       <c r="D294" s="10" t="s">
         <v>248</v>
@@ -21964,13 +21993,13 @@
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="10" t="s">
-        <v>1665</v>
+        <v>1669</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C295" s="10" t="s">
-        <v>1666</v>
+        <v>1670</v>
       </c>
       <c r="D295" s="10" t="s">
         <v>249</v>
@@ -21993,13 +22022,13 @@
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="10" t="s">
-        <v>1667</v>
+        <v>1671</v>
       </c>
       <c r="B296" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>1668</v>
+        <v>1672</v>
       </c>
       <c r="D296" s="10" t="s">
         <v>250</v>
@@ -22022,13 +22051,13 @@
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="10" t="s">
-        <v>1669</v>
+        <v>1673</v>
       </c>
       <c r="B297" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C297" s="10" t="s">
-        <v>1670</v>
+        <v>1674</v>
       </c>
       <c r="D297" s="10" t="s">
         <v>251</v>
@@ -22051,13 +22080,13 @@
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="10" t="s">
-        <v>1671</v>
+        <v>1675</v>
       </c>
       <c r="B298" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C298" s="10" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="D298" s="10" t="s">
         <v>252</v>
@@ -22080,13 +22109,13 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="10" t="s">
-        <v>1673</v>
+        <v>1677</v>
       </c>
       <c r="B299" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="C299" s="10" t="s">
-        <v>1674</v>
+        <v>1678</v>
       </c>
       <c r="D299" s="10" t="s">
         <v>253</v>
@@ -22109,16 +22138,16 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="10" t="s">
-        <v>1675</v>
+        <v>1679</v>
       </c>
       <c r="B300" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C300" s="10" t="s">
-        <v>1677</v>
+        <v>1681</v>
       </c>
       <c r="D300" s="10" t="s">
-        <v>1678</v>
+        <v>1682</v>
       </c>
       <c r="G300" s="36" t="n">
         <f aca="false">Revenue_Build!K7-SUM(Revenue_Build!C7:F7)</f>
@@ -22131,16 +22160,16 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="10" t="s">
-        <v>1679</v>
+        <v>1683</v>
       </c>
       <c r="B301" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C301" s="10" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="D301" s="10" t="s">
-        <v>1681</v>
+        <v>1685</v>
       </c>
       <c r="G301" s="36" t="n">
         <f aca="false">Opex!L16-SUM(Opex!G16:J16)</f>
@@ -22153,16 +22182,16 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="10" t="s">
-        <v>1682</v>
+        <v>1686</v>
       </c>
       <c r="B302" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C302" s="10" t="s">
-        <v>1683</v>
+        <v>1687</v>
       </c>
       <c r="D302" s="10" t="s">
-        <v>1684</v>
+        <v>1688</v>
       </c>
       <c r="G302" s="36" t="n">
         <f aca="false">Opex!C16+Opex!D16-(Historical_Drivers!$O$16+Historical_Drivers!$P$16)/1000</f>
@@ -22175,16 +22204,16 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="10" t="s">
-        <v>1685</v>
+        <v>1689</v>
       </c>
       <c r="B303" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C303" s="10" t="s">
-        <v>1686</v>
+        <v>1690</v>
       </c>
       <c r="D303" s="10" t="s">
-        <v>1687</v>
+        <v>1691</v>
       </c>
       <c r="G303" s="36" t="n">
         <f aca="false">PnL!C17</f>
@@ -22197,16 +22226,16 @@
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="10" t="s">
-        <v>1688</v>
+        <v>1692</v>
       </c>
       <c r="B304" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C304" s="10" t="s">
-        <v>1689</v>
+        <v>1693</v>
       </c>
       <c r="D304" s="10" t="s">
-        <v>1690</v>
+        <v>1694</v>
       </c>
       <c r="G304" s="36" t="n">
         <f aca="false">PnL!D17</f>
@@ -22219,16 +22248,16 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="10" t="s">
-        <v>1691</v>
+        <v>1695</v>
       </c>
       <c r="B305" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C305" s="10" t="s">
-        <v>1692</v>
+        <v>1696</v>
       </c>
       <c r="D305" s="10" t="s">
-        <v>1693</v>
+        <v>1697</v>
       </c>
       <c r="G305" s="36" t="n">
         <f aca="false">Cash_FCF!J15-Cash_FCF!D15-SUM(Cash_FCF!E14:J14)</f>
@@ -22241,16 +22270,16 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="10" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="B306" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C306" s="10" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="D306" s="10" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="G306" s="36" t="n">
         <f aca="false">Revenue_Build!K16-SUM(Revenue_Build!C16:F16)</f>
@@ -22263,16 +22292,16 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="10" t="s">
-        <v>1697</v>
+        <v>1701</v>
       </c>
       <c r="B307" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C307" s="10" t="s">
-        <v>1698</v>
+        <v>1702</v>
       </c>
       <c r="D307" s="10" t="s">
-        <v>1699</v>
+        <v>1703</v>
       </c>
       <c r="G307" s="36" t="n">
         <f aca="false">Opex!L31-SUM(Opex!G31:J31)</f>
@@ -22285,16 +22314,16 @@
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="10" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="B308" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C308" s="10" t="s">
-        <v>1701</v>
+        <v>1705</v>
       </c>
       <c r="D308" s="10" t="s">
-        <v>1702</v>
+        <v>1706</v>
       </c>
       <c r="G308" s="36" t="n">
         <f aca="false">Opex!C31+Opex!D31-(Historical_Drivers!$O$16+Historical_Drivers!$P$16)/1000</f>
@@ -22307,16 +22336,16 @@
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="10" t="s">
-        <v>1703</v>
+        <v>1707</v>
       </c>
       <c r="B309" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C309" s="10" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="D309" s="10" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="G309" s="36" t="n">
         <f aca="false">PnL!C32</f>
@@ -22329,16 +22358,16 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="10" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="B310" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C310" s="10" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="D310" s="10" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
       <c r="G310" s="36" t="n">
         <f aca="false">PnL!D32</f>
@@ -22351,16 +22380,16 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="10" t="s">
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="B311" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C311" s="10" t="s">
-        <v>1710</v>
+        <v>1714</v>
       </c>
       <c r="D311" s="10" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
       <c r="G311" s="36" t="n">
         <f aca="false">Cash_FCF!J29-Cash_FCF!D29-SUM(Cash_FCF!E28:J28)</f>
@@ -22373,16 +22402,16 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="10" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="B312" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C312" s="10" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="D312" s="10" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="G312" s="36" t="n">
         <f aca="false">Revenue_Build!K25-SUM(Revenue_Build!C25:F25)</f>
@@ -22395,16 +22424,16 @@
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="10" t="s">
-        <v>1715</v>
+        <v>1719</v>
       </c>
       <c r="B313" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C313" s="10" t="s">
-        <v>1716</v>
+        <v>1720</v>
       </c>
       <c r="D313" s="10" t="s">
-        <v>1717</v>
+        <v>1721</v>
       </c>
       <c r="G313" s="36" t="n">
         <f aca="false">Opex!L46-SUM(Opex!G46:J46)</f>
@@ -22417,16 +22446,16 @@
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="10" t="s">
-        <v>1718</v>
+        <v>1722</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C314" s="10" t="s">
-        <v>1719</v>
+        <v>1723</v>
       </c>
       <c r="D314" s="10" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="G314" s="36" t="n">
         <f aca="false">Opex!C46+Opex!D46-(Historical_Drivers!$O$16+Historical_Drivers!$P$16)/1000</f>
@@ -22439,16 +22468,16 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="10" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C315" s="10" t="s">
-        <v>1722</v>
+        <v>1726</v>
       </c>
       <c r="D315" s="10" t="s">
-        <v>1723</v>
+        <v>1727</v>
       </c>
       <c r="G315" s="36" t="n">
         <f aca="false">PnL!C47</f>
@@ -22461,16 +22490,16 @@
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="10" t="s">
-        <v>1724</v>
+        <v>1728</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C316" s="10" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="D316" s="10" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="G316" s="36" t="n">
         <f aca="false">PnL!D47</f>
@@ -22483,16 +22512,16 @@
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="10" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="B317" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C317" s="10" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="D317" s="10" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="G317" s="36" t="n">
         <f aca="false">Cash_FCF!J43-Cash_FCF!D43-SUM(Cash_FCF!E42:J42)</f>
@@ -22505,16 +22534,16 @@
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="10" t="s">
-        <v>1730</v>
+        <v>1734</v>
       </c>
       <c r="B318" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C318" s="10" t="s">
-        <v>1731</v>
+        <v>1735</v>
       </c>
       <c r="D318" s="10" t="s">
-        <v>1732</v>
+        <v>1736</v>
       </c>
       <c r="G318" s="36" t="n">
         <f aca="false">Revenue_Build!E7-Historical_Drivers!$C$52</f>
@@ -22527,16 +22556,16 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="10" t="s">
-        <v>1733</v>
+        <v>1737</v>
       </c>
       <c r="B319" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C319" s="10" t="s">
-        <v>1734</v>
+        <v>1738</v>
       </c>
       <c r="D319" s="10" t="s">
-        <v>1735</v>
+        <v>1739</v>
       </c>
       <c r="G319" s="36" t="n">
         <f aca="false">Opex!E16-Historical_Drivers!$C$54</f>
@@ -22549,16 +22578,16 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="10" t="s">
-        <v>1736</v>
+        <v>1740</v>
       </c>
       <c r="B320" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C320" s="10" t="s">
-        <v>1737</v>
+        <v>1741</v>
       </c>
       <c r="D320" s="10" t="s">
-        <v>1738</v>
+        <v>1742</v>
       </c>
       <c r="G320" s="36" t="n">
         <f aca="false">Opex!E31-Historical_Drivers!$C$54</f>
@@ -22571,16 +22600,16 @@
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="10" t="s">
-        <v>1739</v>
+        <v>1743</v>
       </c>
       <c r="B321" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C321" s="10" t="s">
-        <v>1740</v>
+        <v>1744</v>
       </c>
       <c r="D321" s="10" t="s">
-        <v>1741</v>
+        <v>1745</v>
       </c>
       <c r="G321" s="36" t="n">
         <f aca="false">Opex!E46-Historical_Drivers!$C$55</f>
@@ -22593,16 +22622,16 @@
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="10" t="s">
-        <v>1742</v>
+        <v>1746</v>
       </c>
       <c r="B322" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C322" s="10" t="s">
-        <v>1743</v>
+        <v>1747</v>
       </c>
       <c r="D322" s="10" t="s">
-        <v>1744</v>
+        <v>1748</v>
       </c>
       <c r="G322" s="36" t="n">
         <f aca="false">Cash_FCF!K16</f>
@@ -22615,16 +22644,16 @@
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="10" t="s">
-        <v>1745</v>
+        <v>1749</v>
       </c>
       <c r="B323" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C323" s="10" t="s">
-        <v>1746</v>
+        <v>1750</v>
       </c>
       <c r="D323" s="10" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G323" s="36" t="n">
         <f aca="false">Opex!L30-Opex!L15</f>
@@ -22637,16 +22666,16 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="10" t="s">
-        <v>1748</v>
+        <v>1752</v>
       </c>
       <c r="B324" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C324" s="10" t="s">
-        <v>1749</v>
+        <v>1753</v>
       </c>
       <c r="D324" s="10" t="s">
-        <v>1750</v>
+        <v>1754</v>
       </c>
       <c r="G324" s="36" t="n">
         <f aca="false">Scenarios!B21</f>
@@ -22659,16 +22688,16 @@
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="10" t="s">
-        <v>1751</v>
+        <v>1755</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C325" s="10" t="s">
-        <v>1752</v>
+        <v>1756</v>
       </c>
       <c r="D325" s="10" t="s">
-        <v>1753</v>
+        <v>1757</v>
       </c>
       <c r="G325" s="36" t="n">
         <f aca="false">Scenarios!B28</f>
@@ -22681,16 +22710,16 @@
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="10" t="s">
-        <v>1754</v>
+        <v>1758</v>
       </c>
       <c r="B326" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C326" s="10" t="s">
-        <v>1755</v>
+        <v>1759</v>
       </c>
       <c r="D326" s="10" t="s">
-        <v>1756</v>
+        <v>1760</v>
       </c>
       <c r="G326" s="36" t="n">
         <f aca="false">Management_Response!L31</f>
@@ -22703,16 +22732,16 @@
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="10" t="s">
-        <v>1757</v>
+        <v>1761</v>
       </c>
       <c r="B327" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C327" s="10" t="s">
-        <v>1758</v>
+        <v>1762</v>
       </c>
       <c r="D327" s="10" t="s">
-        <v>1759</v>
+        <v>1763</v>
       </c>
       <c r="G327" s="36" t="n">
         <f aca="false">Management_Response!C62-Management_Response!L9-Management_Response!L10</f>
@@ -22725,16 +22754,16 @@
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="10" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="B328" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C328" s="10" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="D328" s="10" t="s">
-        <v>1762</v>
+        <v>1766</v>
       </c>
       <c r="G328" s="36" t="n">
         <f aca="false">Historical_Drivers!$N$26+Cash_Bridge!B58+Cash_Bridge!B54+Cash_Bridge!B55-Historical_Drivers!$P$26</f>
@@ -22747,16 +22776,16 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="10" t="s">
-        <v>1763</v>
+        <v>1767</v>
       </c>
       <c r="B329" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C329" s="10" t="s">
-        <v>1764</v>
+        <v>1768</v>
       </c>
       <c r="D329" s="10" t="s">
-        <v>1765</v>
+        <v>1769</v>
       </c>
       <c r="G329" s="36" t="n">
         <f aca="false">Cash_Bridge!B56+Cash_Bridge!B57+Cash_Bridge!B32+Cash_Bridge!B33+Cash_Bridge!B34+Cash_Bridge!B47+Cash_Bridge!B48-Cash_Bridge!B54</f>
@@ -22769,16 +22798,16 @@
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="10" t="s">
-        <v>1766</v>
+        <v>1770</v>
       </c>
       <c r="B330" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C330" s="10" t="s">
-        <v>1767</v>
+        <v>1771</v>
       </c>
       <c r="D330" s="10" t="s">
-        <v>1768</v>
+        <v>1772</v>
       </c>
       <c r="G330" s="36" t="n">
         <f aca="false">Cash_Bridge!B35+Cash_Bridge!B36+Cash_Bridge!B31-Cash_Bridge!B55</f>
@@ -22791,16 +22820,16 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="10" t="s">
-        <v>1769</v>
+        <v>1773</v>
       </c>
       <c r="B331" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C331" s="10" t="s">
-        <v>1770</v>
+        <v>1774</v>
       </c>
       <c r="D331" s="10" t="s">
-        <v>1771</v>
+        <v>1775</v>
       </c>
       <c r="G331" s="36" t="n">
         <f aca="false">Cash_Bridge!B18-Cash_Bridge!B19</f>
@@ -22813,16 +22842,16 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="10" t="s">
-        <v>1772</v>
+        <v>1776</v>
       </c>
       <c r="B332" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C332" s="10" t="s">
-        <v>1773</v>
+        <v>1777</v>
       </c>
       <c r="D332" s="10" t="s">
-        <v>1774</v>
+        <v>1778</v>
       </c>
       <c r="G332" s="36" t="n">
         <f aca="false">Cash_Bridge!D18-Cash_Bridge!D19</f>
@@ -22835,16 +22864,16 @@
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="10" t="s">
-        <v>1775</v>
+        <v>1779</v>
       </c>
       <c r="B333" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C333" s="10" t="s">
-        <v>1776</v>
+        <v>1780</v>
       </c>
       <c r="D333" s="10" t="s">
-        <v>1777</v>
+        <v>1781</v>
       </c>
       <c r="G333" s="36" t="n">
         <f aca="false">Cash_Bridge!B49-Cash_Bridge!B50</f>
@@ -22857,16 +22886,16 @@
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="10" t="s">
-        <v>1778</v>
+        <v>1782</v>
       </c>
       <c r="B334" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C334" s="10" t="s">
-        <v>1779</v>
+        <v>1783</v>
       </c>
       <c r="D334" s="10" t="s">
-        <v>1780</v>
+        <v>1784</v>
       </c>
       <c r="G334" s="36" t="n">
         <f aca="false">IF(ABS(Cash_Bridge!B39)&lt;5000,0,Cash_Bridge!B39)</f>
@@ -22879,16 +22908,16 @@
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="10" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="B335" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C335" s="10" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
       <c r="D335" s="10" t="s">
-        <v>1783</v>
+        <v>1787</v>
       </c>
       <c r="G335" s="36" t="n">
         <f aca="false">SUMPRODUCT(ISNUMBER(Historical_Drivers!C38:P38)*NOT(ISNUMBER(Historical_Drivers!C28:P28)))</f>
@@ -22901,16 +22930,16 @@
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="10" t="s">
-        <v>1784</v>
+        <v>1788</v>
       </c>
       <c r="B336" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C336" s="10" t="s">
-        <v>1785</v>
+        <v>1789</v>
       </c>
       <c r="D336" s="10" t="s">
-        <v>1786</v>
+        <v>1790</v>
       </c>
       <c r="G336" s="36" t="n">
         <f aca="false">Cash_FCF!K11-Cash_FCF!K7-Cash_FCF!K10</f>
@@ -22923,16 +22952,16 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="10" t="s">
-        <v>1787</v>
+        <v>1791</v>
       </c>
       <c r="B337" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C337" s="10" t="s">
-        <v>1788</v>
+        <v>1792</v>
       </c>
       <c r="D337" s="10" t="s">
-        <v>1789</v>
+        <v>1793</v>
       </c>
       <c r="G337" s="36" t="n">
         <f aca="false">Trigger_History!$E$36-Historical_Drivers!$C$65</f>
@@ -22945,16 +22974,16 @@
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="10" t="s">
-        <v>1790</v>
+        <v>1794</v>
       </c>
       <c r="B338" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C338" s="10" t="s">
-        <v>1791</v>
+        <v>1795</v>
       </c>
       <c r="D338" s="10" t="s">
-        <v>1792</v>
+        <v>1796</v>
       </c>
       <c r="G338" s="36" t="n">
         <f aca="false">Trigger_History!H38-Assumptions!$D$19</f>
@@ -22967,16 +22996,16 @@
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="10" t="s">
-        <v>1793</v>
+        <v>1797</v>
       </c>
       <c r="B339" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C339" s="10" t="s">
-        <v>1794</v>
+        <v>1798</v>
       </c>
       <c r="D339" s="10" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
       <c r="G339" s="36" t="n">
         <f aca="false">SUMPRODUCT((Management_Response!G7:J7&lt;Management_Response!$C$4)*Management_Response!G11:J11)</f>
@@ -22989,16 +23018,16 @@
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="10" t="s">
-        <v>1796</v>
+        <v>1800</v>
       </c>
       <c r="B340" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C340" s="10" t="s">
-        <v>1797</v>
+        <v>1801</v>
       </c>
       <c r="D340" s="10" t="s">
-        <v>1798</v>
+        <v>1802</v>
       </c>
       <c r="G340" s="36" t="n">
         <f aca="false">Management_Response!E17*Management_Response!E16-Management_Response!E15</f>
@@ -23011,16 +23040,16 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="10" t="s">
-        <v>1799</v>
+        <v>1803</v>
       </c>
       <c r="B341" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C341" s="10" t="s">
-        <v>1800</v>
+        <v>1804</v>
       </c>
       <c r="D341" s="10" t="s">
-        <v>1801</v>
+        <v>1805</v>
       </c>
       <c r="G341" s="36" t="n">
         <f aca="false">Scenarios!B49+Scenarios!B50-Scenarios!B48</f>
@@ -23033,16 +23062,16 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="10" t="s">
-        <v>1802</v>
+        <v>1806</v>
       </c>
       <c r="B342" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C342" s="10" t="s">
-        <v>1803</v>
+        <v>1807</v>
       </c>
       <c r="D342" s="10" t="s">
-        <v>1804</v>
+        <v>1808</v>
       </c>
       <c r="G342" s="36" t="n">
         <f aca="false">Revenue_Build!E48-Revenue_Build!E7</f>
@@ -23055,16 +23084,16 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="10" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C343" s="10" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
       <c r="D343" s="10" t="s">
-        <v>1807</v>
+        <v>1811</v>
       </c>
       <c r="G343" s="36" t="n">
         <f aca="false">IF(AND(Revenue_Build!L38&lt;=Revenue_Build!L7,Revenue_Build!L7&lt;=Revenue_Build!L39),0,1)</f>
@@ -23077,7 +23106,7 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="10" t="s">
-        <v>1808</v>
+        <v>1812</v>
       </c>
       <c r="B345" s="10" t="str">
         <f aca="false">COUNTIF(H4:H343,"PASS")&amp;" PASS / "&amp;COUNTIF(H4:H343,"FAIL")&amp;" FAIL"</f>
@@ -23086,18 +23115,18 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="2" t="s">
-        <v>1809</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="2" t="s">
-        <v>1810</v>
+        <v>1814</v>
       </c>
       <c r="B348" s="37" t="s">
-        <v>1811</v>
+        <v>1815</v>
       </c>
       <c r="C348" s="19" t="s">
-        <v>1812</v>
+        <v>1816</v>
       </c>
       <c r="D348" s="19"/>
       <c r="E348" s="19"/>
@@ -23107,13 +23136,13 @@
     </row>
     <row r="349" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="2" t="s">
-        <v>1813</v>
+        <v>1817</v>
       </c>
       <c r="B349" s="37" t="s">
-        <v>1811</v>
+        <v>1815</v>
       </c>
       <c r="C349" s="19" t="s">
-        <v>1814</v>
+        <v>1818</v>
       </c>
       <c r="D349" s="19"/>
       <c r="E349" s="19"/>
@@ -23123,13 +23152,13 @@
     </row>
     <row r="350" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B350" s="37" t="s">
         <v>1815</v>
       </c>
-      <c r="B350" s="37" t="s">
-        <v>1811</v>
-      </c>
       <c r="C350" s="19" t="s">
-        <v>1816</v>
+        <v>1820</v>
       </c>
       <c r="D350" s="19"/>
       <c r="E350" s="19"/>
@@ -23139,13 +23168,13 @@
     </row>
     <row r="351" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="2" t="s">
-        <v>1817</v>
+        <v>1821</v>
       </c>
       <c r="B351" s="32" t="s">
-        <v>1818</v>
+        <v>1822</v>
       </c>
       <c r="C351" s="19" t="s">
-        <v>1819</v>
+        <v>1823</v>
       </c>
       <c r="D351" s="19"/>
       <c r="E351" s="19"/>
@@ -23155,13 +23184,13 @@
     </row>
     <row r="352" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="2" t="s">
-        <v>1820</v>
+        <v>1824</v>
       </c>
       <c r="B352" s="37" t="s">
-        <v>1811</v>
+        <v>1815</v>
       </c>
       <c r="C352" s="19" t="s">
-        <v>1821</v>
+        <v>1825</v>
       </c>
       <c r="D352" s="19"/>
       <c r="E352" s="19"/>
@@ -23171,13 +23200,13 @@
     </row>
     <row r="353" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="2" t="s">
-        <v>1822</v>
+        <v>1826</v>
       </c>
       <c r="B353" s="37" t="s">
-        <v>1811</v>
+        <v>1815</v>
       </c>
       <c r="C353" s="19" t="s">
-        <v>1823</v>
+        <v>1827</v>
       </c>
       <c r="D353" s="19"/>
       <c r="E353" s="19"/>
@@ -23187,13 +23216,13 @@
     </row>
     <row r="354" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="2" t="s">
-        <v>1824</v>
+        <v>1828</v>
       </c>
       <c r="B354" s="37" t="s">
-        <v>1811</v>
+        <v>1815</v>
       </c>
       <c r="C354" s="19" t="s">
-        <v>1825</v>
+        <v>1829</v>
       </c>
       <c r="D354" s="19"/>
       <c r="E354" s="19"/>
@@ -23238,7 +23267,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>1826</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23249,13 +23278,13 @@
         <v>263</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1827</v>
+        <v>1831</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>901</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>365</v>
@@ -23266,7 +23295,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1828</v>
+        <v>1832</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>266</v>
@@ -23276,15 +23305,15 @@
         <v>378.38245825603</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1829</v>
+        <v>1833</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>1831</v>
+        <v>1835</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>266</v>
@@ -23294,15 +23323,15 @@
         <v>69.637</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>1829</v>
+        <v>1833</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>440</v>
@@ -23315,12 +23344,12 @@
         <v>256</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>266</v>
@@ -23330,15 +23359,15 @@
         <v>56.9095409524635</v>
       </c>
       <c r="F7" s="10" t="s">
+        <v>1838</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>1834</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>1830</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>1835</v>
+        <v>1839</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>440</v>
@@ -23348,33 +23377,33 @@
         <v>1.085</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1836</v>
+        <v>1840</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>1837</v>
+        <v>1841</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1838</v>
+        <v>1842</v>
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">Revenue_Build!E11</f>
         <v>5110.5</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>1839</v>
+        <v>1843</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>1840</v>
+        <v>1844</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>266</v>
@@ -23384,10 +23413,10 @@
         <v>1123.23804095246</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>1841</v>
+        <v>1845</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
     </row>
   </sheetData>
